--- a/Dados_simulacoes_motores.xlsx
+++ b/Dados_simulacoes_motores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjona\Desktop\arquivos github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94931761-C659-419A-9CCC-A62EF809C4A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E446DFF-5428-4F20-A940-FBDA7845EAAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="2370" windowWidth="20730" windowHeight="11160" xr2:uid="{F9989169-A565-4D05-8CA6-494653461A7A}"/>
   </bookViews>
@@ -266,7 +266,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -311,11 +311,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -412,16 +436,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -433,10 +454,31 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -6414,13 +6456,13 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>3.1708054698461025E-2</c:v>
+                  <c:v>2.5187149400354443E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.42130608621378796</c:v>
+                  <c:v>0.42219598884605858</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.74513000622539816</c:v>
+                  <c:v>0.73790465950416517</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6485,13 +6527,13 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>0.91489866644652562</c:v>
+                  <c:v>0.87915227224370118</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.84202833638755858</c:v>
+                  <c:v>0.86559721366277897</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.20731605012714002</c:v>
+                  <c:v>0.20880961926935107</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6553,13 +6595,13 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>0.55171624488197313</c:v>
+                  <c:v>0.53991986787472024</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.2612864587999946</c:v>
+                  <c:v>1.2450734089052302</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.88668720252318411</c:v>
+                  <c:v>0.92244980086342498</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6619,13 +6661,13 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>0.39145746541309273</c:v>
+                  <c:v>0.31095246173276614</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.41438328474331115</c:v>
+                  <c:v>0.4249773636989182</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.28910754931683291</c:v>
+                  <c:v>0.24188000920531078</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10156,13 +10198,13 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>2.912151201625379E-4</c:v>
+                  <c:v>2.3139767682546885E-4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.9523507127199303E-5</c:v>
+                  <c:v>1.231596769411647E-5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>9.1263575915187186E-4</c:v>
+                  <c:v>9.3181851444638973E-4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10222,13 +10264,13 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>1.5665932257478855E-3</c:v>
+                  <c:v>1.5175606732554115E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5.4055127628596595E-3</c:v>
+                  <c:v>5.3554221063705151E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>8.7539893919115486E-4</c:v>
+                  <c:v>7.8682496022633441E-4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10321,13 +10363,13 @@
                       <c:formatCode>0.0000</c:formatCode>
                       <c:ptCount val="3"/>
                       <c:pt idx="0">
-                        <c:v>3.1708054698461025E-2</c:v>
+                        <c:v>2.5187149400354443E-2</c:v>
                       </c:pt>
                       <c:pt idx="1">
-                        <c:v>0.42130608621378796</c:v>
+                        <c:v>0.42219598884605858</c:v>
                       </c:pt>
                       <c:pt idx="2">
-                        <c:v>0.74513000622539816</c:v>
+                        <c:v>0.73790465950416517</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -10407,13 +10449,13 @@
                       <c:formatCode>0.0000</c:formatCode>
                       <c:ptCount val="3"/>
                       <c:pt idx="0">
-                        <c:v>0.91489866644652562</c:v>
+                        <c:v>0.87915227224370118</c:v>
                       </c:pt>
                       <c:pt idx="1">
-                        <c:v>0.84202833638755858</c:v>
+                        <c:v>0.86559721366277897</c:v>
                       </c:pt>
                       <c:pt idx="2">
-                        <c:v>0.20731605012714002</c:v>
+                        <c:v>0.20880961926935107</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -10493,13 +10535,13 @@
                       <c:formatCode>0.0000</c:formatCode>
                       <c:ptCount val="3"/>
                       <c:pt idx="0">
-                        <c:v>0.55171624488197313</c:v>
+                        <c:v>0.53991986787472024</c:v>
                       </c:pt>
                       <c:pt idx="1">
-                        <c:v>1.2612864587999946</c:v>
+                        <c:v>1.2450734089052302</c:v>
                       </c:pt>
                       <c:pt idx="2">
-                        <c:v>0.88668720252318411</c:v>
+                        <c:v>0.92244980086342498</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -10579,13 +10621,13 @@
                       <c:formatCode>0.0000</c:formatCode>
                       <c:ptCount val="3"/>
                       <c:pt idx="0">
-                        <c:v>0.39145746541309273</c:v>
+                        <c:v>0.31095246173276614</c:v>
                       </c:pt>
                       <c:pt idx="1">
-                        <c:v>0.41438328474331115</c:v>
+                        <c:v>0.4249773636989182</c:v>
                       </c:pt>
                       <c:pt idx="2">
-                        <c:v>0.28910754931683291</c:v>
+                        <c:v>0.24188000920531078</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -19941,58 +19983,58 @@
   </cols>
   <sheetData>
     <row r="4" spans="6:115" x14ac:dyDescent="0.25">
-      <c r="L4" s="34" t="s">
+      <c r="L4" s="41" t="s">
         <v>40</v>
       </c>
-      <c r="M4" s="34"/>
-      <c r="N4" s="34"/>
-      <c r="O4" s="34"/>
-      <c r="P4" s="34"/>
-      <c r="Q4" s="34"/>
-      <c r="R4" s="34"/>
-      <c r="AJ4" s="34" t="s">
+      <c r="M4" s="41"/>
+      <c r="N4" s="41"/>
+      <c r="O4" s="41"/>
+      <c r="P4" s="41"/>
+      <c r="Q4" s="41"/>
+      <c r="R4" s="41"/>
+      <c r="AJ4" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="AK4" s="34"/>
-      <c r="AL4" s="34"/>
-      <c r="AM4" s="34"/>
-      <c r="AN4" s="34"/>
+      <c r="AK4" s="41"/>
+      <c r="AL4" s="41"/>
+      <c r="AM4" s="41"/>
+      <c r="AN4" s="41"/>
       <c r="AO4" s="33"/>
       <c r="AP4" s="33"/>
       <c r="AQ4" s="33"/>
       <c r="AR4" s="33"/>
       <c r="AS4" s="33"/>
-      <c r="BG4" s="34" t="s">
+      <c r="BG4" s="41" t="s">
         <v>38</v>
       </c>
-      <c r="BH4" s="34"/>
-      <c r="BI4" s="34"/>
-      <c r="BJ4" s="34"/>
-      <c r="BK4" s="34"/>
+      <c r="BH4" s="41"/>
+      <c r="BI4" s="41"/>
+      <c r="BJ4" s="41"/>
+      <c r="BK4" s="41"/>
       <c r="BL4" s="33"/>
       <c r="BM4" s="33"/>
       <c r="BN4" s="33"/>
       <c r="BO4" s="33"/>
-      <c r="CC4" s="34" t="s">
+      <c r="CC4" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="CD4" s="34"/>
-      <c r="CE4" s="34"/>
-      <c r="CF4" s="34"/>
+      <c r="CD4" s="41"/>
+      <c r="CE4" s="41"/>
+      <c r="CF4" s="41"/>
       <c r="CG4" s="33"/>
       <c r="CH4" s="33"/>
       <c r="CI4" s="33"/>
       <c r="CJ4" s="33"/>
       <c r="CK4" s="33"/>
       <c r="CL4" s="33"/>
-      <c r="CY4" s="34" t="s">
+      <c r="CY4" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="CZ4" s="34"/>
-      <c r="DA4" s="34"/>
-      <c r="DB4" s="34"/>
-      <c r="DC4" s="34"/>
-      <c r="DD4" s="34"/>
+      <c r="CZ4" s="41"/>
+      <c r="DA4" s="41"/>
+      <c r="DB4" s="41"/>
+      <c r="DC4" s="41"/>
+      <c r="DD4" s="41"/>
       <c r="DE4" s="33"/>
       <c r="DF4" s="33"/>
       <c r="DG4" s="33"/>
@@ -20004,18 +20046,18 @@
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
-      <c r="K6" s="42" t="s">
+      <c r="K6" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="L6" s="42"/>
-      <c r="M6" s="42"/>
-      <c r="N6" s="42"/>
-      <c r="O6" s="42"/>
-      <c r="P6" s="42"/>
-      <c r="Q6" s="42"/>
-      <c r="R6" s="42"/>
-      <c r="S6" s="42"/>
-      <c r="T6" s="42"/>
+      <c r="L6" s="35"/>
+      <c r="M6" s="35"/>
+      <c r="N6" s="35"/>
+      <c r="O6" s="35"/>
+      <c r="P6" s="35"/>
+      <c r="Q6" s="35"/>
+      <c r="R6" s="35"/>
+      <c r="S6" s="35"/>
+      <c r="T6" s="35"/>
       <c r="U6" s="1"/>
       <c r="V6" s="1"/>
       <c r="W6" s="1"/>
@@ -20026,18 +20068,18 @@
       <c r="AF6" s="1"/>
       <c r="AG6" s="1"/>
       <c r="AH6" s="1"/>
-      <c r="AI6" s="42" t="s">
+      <c r="AI6" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="AJ6" s="42"/>
-      <c r="AK6" s="42"/>
-      <c r="AL6" s="42"/>
-      <c r="AM6" s="42"/>
-      <c r="AN6" s="42"/>
-      <c r="AO6" s="42"/>
-      <c r="AP6" s="42"/>
-      <c r="AQ6" s="42"/>
-      <c r="AR6" s="42"/>
+      <c r="AJ6" s="35"/>
+      <c r="AK6" s="35"/>
+      <c r="AL6" s="35"/>
+      <c r="AM6" s="35"/>
+      <c r="AN6" s="35"/>
+      <c r="AO6" s="35"/>
+      <c r="AP6" s="35"/>
+      <c r="AQ6" s="35"/>
+      <c r="AR6" s="35"/>
       <c r="AS6" s="1"/>
       <c r="AT6" s="1"/>
       <c r="AU6" s="1"/>
@@ -20047,18 +20089,18 @@
       <c r="BC6" s="1"/>
       <c r="BD6" s="1"/>
       <c r="BE6" s="1"/>
-      <c r="BF6" s="42" t="s">
+      <c r="BF6" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="BG6" s="42"/>
-      <c r="BH6" s="42"/>
-      <c r="BI6" s="42"/>
-      <c r="BJ6" s="42"/>
-      <c r="BK6" s="42"/>
-      <c r="BL6" s="42"/>
-      <c r="BM6" s="42"/>
-      <c r="BN6" s="42"/>
-      <c r="BO6" s="42"/>
+      <c r="BG6" s="35"/>
+      <c r="BH6" s="35"/>
+      <c r="BI6" s="35"/>
+      <c r="BJ6" s="35"/>
+      <c r="BK6" s="35"/>
+      <c r="BL6" s="35"/>
+      <c r="BM6" s="35"/>
+      <c r="BN6" s="35"/>
+      <c r="BO6" s="35"/>
       <c r="BP6" s="1"/>
       <c r="BQ6" s="1"/>
       <c r="BR6" s="1"/>
@@ -20071,187 +20113,187 @@
       <c r="CB6" s="1"/>
       <c r="CC6" s="1"/>
       <c r="CD6" s="1"/>
-      <c r="CE6" s="42" t="s">
+      <c r="CE6" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="CF6" s="42"/>
-      <c r="CG6" s="42"/>
-      <c r="CH6" s="42"/>
-      <c r="CI6" s="42"/>
-      <c r="CJ6" s="42"/>
-      <c r="CK6" s="42"/>
-      <c r="CL6" s="42"/>
-      <c r="CM6" s="42"/>
-      <c r="CN6" s="42"/>
-      <c r="DA6" s="42" t="s">
+      <c r="CF6" s="35"/>
+      <c r="CG6" s="35"/>
+      <c r="CH6" s="35"/>
+      <c r="CI6" s="35"/>
+      <c r="CJ6" s="35"/>
+      <c r="CK6" s="35"/>
+      <c r="CL6" s="35"/>
+      <c r="CM6" s="35"/>
+      <c r="CN6" s="35"/>
+      <c r="DA6" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="DB6" s="42"/>
-      <c r="DC6" s="42"/>
-      <c r="DD6" s="42"/>
-      <c r="DE6" s="42"/>
-      <c r="DF6" s="42"/>
-      <c r="DG6" s="42"/>
-      <c r="DH6" s="42"/>
-      <c r="DI6" s="42"/>
-      <c r="DJ6" s="42"/>
+      <c r="DB6" s="35"/>
+      <c r="DC6" s="35"/>
+      <c r="DD6" s="35"/>
+      <c r="DE6" s="35"/>
+      <c r="DF6" s="35"/>
+      <c r="DG6" s="35"/>
+      <c r="DH6" s="35"/>
+      <c r="DI6" s="35"/>
+      <c r="DJ6" s="35"/>
     </row>
     <row r="7" spans="6:115" ht="15.75" x14ac:dyDescent="0.25">
       <c r="F7" s="1"/>
       <c r="G7" s="36" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="H7" s="36"/>
       <c r="I7" s="36"/>
-      <c r="J7" s="37" t="s">
+      <c r="J7" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="K7" s="37"/>
-      <c r="L7" s="37"/>
-      <c r="M7" s="38" t="s">
+      <c r="K7" s="40"/>
+      <c r="L7" s="40"/>
+      <c r="M7" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="N7" s="38"/>
-      <c r="O7" s="38"/>
-      <c r="P7" s="39" t="s">
+      <c r="N7" s="37"/>
+      <c r="O7" s="37"/>
+      <c r="P7" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="Q7" s="39"/>
-      <c r="R7" s="39"/>
-      <c r="S7" s="40" t="s">
+      <c r="Q7" s="38"/>
+      <c r="R7" s="38"/>
+      <c r="S7" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="T7" s="40"/>
-      <c r="U7" s="40"/>
-      <c r="V7" s="41" t="s">
+      <c r="T7" s="47"/>
+      <c r="U7" s="48"/>
+      <c r="V7" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="W7" s="41"/>
-      <c r="X7" s="41"/>
+      <c r="W7" s="44"/>
+      <c r="X7" s="45"/>
       <c r="AC7" s="1"/>
       <c r="AD7" s="36" t="s">
         <v>1</v>
       </c>
       <c r="AE7" s="36"/>
       <c r="AF7" s="36"/>
-      <c r="AG7" s="37" t="s">
+      <c r="AG7" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="AH7" s="37"/>
-      <c r="AI7" s="37"/>
-      <c r="AJ7" s="38" t="s">
+      <c r="AH7" s="40"/>
+      <c r="AI7" s="40"/>
+      <c r="AJ7" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="AK7" s="38"/>
-      <c r="AL7" s="38"/>
-      <c r="AM7" s="39" t="s">
+      <c r="AK7" s="37"/>
+      <c r="AL7" s="37"/>
+      <c r="AM7" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="AN7" s="39"/>
-      <c r="AO7" s="39"/>
-      <c r="AP7" s="40" t="s">
+      <c r="AN7" s="38"/>
+      <c r="AO7" s="38"/>
+      <c r="AP7" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="AQ7" s="40"/>
-      <c r="AR7" s="40"/>
-      <c r="AS7" s="41" t="s">
+      <c r="AQ7" s="39"/>
+      <c r="AR7" s="39"/>
+      <c r="AS7" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="AT7" s="41"/>
-      <c r="AU7" s="41"/>
+      <c r="AT7" s="34"/>
+      <c r="AU7" s="34"/>
       <c r="AZ7" s="1"/>
       <c r="BA7" s="36" t="s">
         <v>1</v>
       </c>
       <c r="BB7" s="36"/>
       <c r="BC7" s="36"/>
-      <c r="BD7" s="37" t="s">
+      <c r="BD7" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="BE7" s="37"/>
-      <c r="BF7" s="37"/>
-      <c r="BG7" s="38" t="s">
+      <c r="BE7" s="40"/>
+      <c r="BF7" s="40"/>
+      <c r="BG7" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="BH7" s="38"/>
-      <c r="BI7" s="38"/>
-      <c r="BJ7" s="39" t="s">
+      <c r="BH7" s="37"/>
+      <c r="BI7" s="37"/>
+      <c r="BJ7" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="BK7" s="39"/>
-      <c r="BL7" s="39"/>
-      <c r="BM7" s="40" t="s">
+      <c r="BK7" s="38"/>
+      <c r="BL7" s="38"/>
+      <c r="BM7" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="BN7" s="40"/>
-      <c r="BO7" s="40"/>
-      <c r="BP7" s="41" t="s">
+      <c r="BN7" s="39"/>
+      <c r="BO7" s="39"/>
+      <c r="BP7" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="BQ7" s="41"/>
-      <c r="BR7" s="41"/>
+      <c r="BQ7" s="34"/>
+      <c r="BR7" s="34"/>
       <c r="BV7" s="1"/>
       <c r="BW7" s="36" t="s">
         <v>1</v>
       </c>
       <c r="BX7" s="36"/>
       <c r="BY7" s="36"/>
-      <c r="BZ7" s="37" t="s">
+      <c r="BZ7" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="CA7" s="37"/>
-      <c r="CB7" s="37"/>
-      <c r="CC7" s="38" t="s">
+      <c r="CA7" s="40"/>
+      <c r="CB7" s="40"/>
+      <c r="CC7" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="CD7" s="38"/>
-      <c r="CE7" s="38"/>
-      <c r="CF7" s="39" t="s">
+      <c r="CD7" s="37"/>
+      <c r="CE7" s="37"/>
+      <c r="CF7" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="CG7" s="39"/>
-      <c r="CH7" s="39"/>
-      <c r="CI7" s="40" t="s">
+      <c r="CG7" s="38"/>
+      <c r="CH7" s="38"/>
+      <c r="CI7" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="CJ7" s="40"/>
-      <c r="CK7" s="40"/>
-      <c r="CL7" s="41" t="s">
+      <c r="CJ7" s="39"/>
+      <c r="CK7" s="39"/>
+      <c r="CL7" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="CM7" s="41"/>
-      <c r="CN7" s="41"/>
+      <c r="CM7" s="34"/>
+      <c r="CN7" s="34"/>
       <c r="CS7" s="1"/>
       <c r="CT7" s="36" t="s">
         <v>1</v>
       </c>
       <c r="CU7" s="36"/>
       <c r="CV7" s="36"/>
-      <c r="CW7" s="37" t="s">
+      <c r="CW7" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="CX7" s="37"/>
-      <c r="CY7" s="37"/>
-      <c r="CZ7" s="38" t="s">
+      <c r="CX7" s="40"/>
+      <c r="CY7" s="40"/>
+      <c r="CZ7" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="DA7" s="38"/>
-      <c r="DB7" s="38"/>
-      <c r="DC7" s="39" t="s">
+      <c r="DA7" s="37"/>
+      <c r="DB7" s="37"/>
+      <c r="DC7" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="DD7" s="39"/>
-      <c r="DE7" s="39"/>
-      <c r="DF7" s="40" t="s">
+      <c r="DD7" s="38"/>
+      <c r="DE7" s="38"/>
+      <c r="DF7" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="DG7" s="40"/>
-      <c r="DH7" s="40"/>
-      <c r="DI7" s="41" t="s">
+      <c r="DG7" s="39"/>
+      <c r="DH7" s="39"/>
+      <c r="DI7" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="DJ7" s="41"/>
-      <c r="DK7" s="41"/>
+      <c r="DJ7" s="34"/>
+      <c r="DK7" s="34"/>
     </row>
     <row r="8" spans="6:115" ht="15.75" x14ac:dyDescent="0.25">
       <c r="F8" s="1" t="s">
@@ -20761,7 +20803,7 @@
         <v>5.7959094839021841E-4</v>
       </c>
       <c r="CL9" s="20">
-        <v>1.9186186363091551E-3</v>
+        <v>1.9186186363091601E-3</v>
       </c>
       <c r="CM9" s="20">
         <v>5.7204987466374924E-3</v>
@@ -27604,58 +27646,58 @@
         <v>25</v>
       </c>
       <c r="BW33" s="15">
-        <v>5.1538249337390617E-2</v>
+        <v>2.4689124855706204E-2</v>
       </c>
       <c r="BX33" s="15">
-        <v>0.41880731861624365</v>
+        <v>0.42255970842234936</v>
       </c>
       <c r="BY33" s="15">
-        <v>0.7631609080930668</v>
+        <v>0.74136434823999642</v>
       </c>
       <c r="BZ33" s="16">
-        <v>0.74462941768640156</v>
+        <v>0.51712394192166911</v>
       </c>
       <c r="CA33" s="16">
-        <v>1.2859400897625279</v>
+        <v>1.2583025891840687</v>
       </c>
       <c r="CB33" s="16">
-        <v>0.64061433285312708</v>
+        <v>0.93935410684458154</v>
       </c>
       <c r="CC33" s="17">
-        <v>1.1339157511541031</v>
+        <v>0.91566641251267056</v>
       </c>
       <c r="CD33" s="17">
-        <v>0.65708301789778578</v>
+        <v>0.88785463347532767</v>
       </c>
       <c r="CE33" s="17">
-        <v>0.13255535101768601</v>
+        <v>0.28892873245293116</v>
       </c>
       <c r="CF33" s="18">
-        <v>0.63627468317762792</v>
+        <v>0.3048040105642571</v>
       </c>
       <c r="CG33" s="18">
-        <v>0.38463605143927804</v>
+        <v>0.42930735865482222</v>
       </c>
       <c r="CH33" s="18">
-        <v>4.4715244137336969E-2</v>
+        <v>0.17999155847174952</v>
       </c>
       <c r="CI33" s="19">
-        <v>4.7339253318656738E-4</v>
+        <v>2.2683705334058946E-4</v>
       </c>
       <c r="CJ33" s="19">
-        <v>2.8824583895636913E-5</v>
+        <v>5.6920786261072109E-6</v>
       </c>
       <c r="CK33" s="19">
-        <v>7.022516037533677E-4</v>
+        <v>9.0039040295275541E-4</v>
       </c>
       <c r="CL33" s="20">
-        <v>2.1374827894778958E-3</v>
+        <v>1.4550466797046413E-3</v>
       </c>
       <c r="CM33" s="20">
-        <v>5.4827982097049865E-3</v>
+        <v>5.4063640263050106E-3</v>
       </c>
       <c r="CN33" s="20">
-        <v>4.6896568610577116E-4</v>
+        <v>7.5849847042142038E-4</v>
       </c>
       <c r="CS33" s="1">
         <v>25</v>
@@ -32196,58 +32238,58 @@
         <v>41</v>
       </c>
       <c r="BW49" s="15">
-        <v>0.16868367483084457</v>
+        <v>2.2720577135283613E-2</v>
       </c>
       <c r="BX49" s="15">
-        <v>0.40602713489233361</v>
+        <v>0.42395350457946979</v>
       </c>
       <c r="BY49" s="15">
-        <v>0.90967498323593599</v>
+        <v>0.73555734130631367</v>
       </c>
       <c r="BZ49" s="16">
-        <v>1.0153467104715284</v>
+        <v>0.51693471466496299</v>
       </c>
       <c r="CA49" s="16">
-        <v>1.6076177690331224</v>
+        <v>1.2331511998529492</v>
       </c>
       <c r="CB49" s="16">
-        <v>7.4261591485360684E-2</v>
+        <v>0.92652661449023588</v>
       </c>
       <c r="CC49" s="17">
-        <v>1.7396575664015339</v>
+        <v>0.84963151121066427</v>
       </c>
       <c r="CD49" s="17">
-        <v>0.41782370131024477</v>
+        <v>0.86476644692426219</v>
       </c>
       <c r="CE49" s="17">
-        <v>0.43444414272016246</v>
+        <v>0.17786403289146879</v>
       </c>
       <c r="CF49" s="18">
-        <v>2.0825145040845534</v>
+        <v>0.28050095228757255</v>
       </c>
       <c r="CG49" s="18">
-        <v>0.23249100710697168</v>
+        <v>0.44590017004913446</v>
       </c>
       <c r="CH49" s="18">
-        <v>1.5551696270533879</v>
+        <v>0.23985760933447209</v>
       </c>
       <c r="CI49" s="19">
-        <v>1.547592435903189E-3</v>
+        <v>2.0875467360659261E-4</v>
       </c>
       <c r="CJ49" s="19">
-        <v>1.4636462744299639E-4</v>
+        <v>1.8513688425425556E-5</v>
       </c>
       <c r="CK49" s="19">
-        <v>6.3187783913021267E-4</v>
+        <v>9.5316356671104607E-4</v>
       </c>
       <c r="CL49" s="20">
-        <v>3.1749058166119504E-3</v>
+        <v>1.4492808100740051E-3</v>
       </c>
       <c r="CM49" s="20">
-        <v>6.4726166852415723E-3</v>
+        <v>5.3302020972256781E-3</v>
       </c>
       <c r="CN49" s="20">
-        <v>3.757659925712864E-3</v>
+        <v>7.31539247257329E-4</v>
       </c>
       <c r="CS49" s="1">
         <v>41</v>
@@ -34205,58 +34247,58 @@
         <v>48</v>
       </c>
       <c r="BW56" s="15">
-        <v>0.17381595575714975</v>
+        <v>2.0582913029066188E-2</v>
       </c>
       <c r="BX56" s="15">
-        <v>0.39914858355824284</v>
+        <v>0.42196495567853193</v>
       </c>
       <c r="BY56" s="15">
-        <v>0.89879514970752938</v>
+        <v>0.73344201542857101</v>
       </c>
       <c r="BZ56" s="16">
-        <v>0.42183935856432603</v>
+        <v>0.55793797977298021</v>
       </c>
       <c r="CA56" s="16">
-        <v>1.6521923277554473</v>
+        <v>1.2436439027758457</v>
       </c>
       <c r="CB56" s="16">
-        <v>0.29933760530513182</v>
+        <v>0.93646272532084474</v>
       </c>
       <c r="CC56" s="17">
-        <v>1.5933015661532282</v>
+        <v>0.91425724984430268</v>
       </c>
       <c r="CD56" s="17">
-        <v>0.37473489814095506</v>
+        <v>0.87546440071042519</v>
       </c>
       <c r="CE56" s="17">
-        <v>9.0181882880835187E-2</v>
+        <v>0.26506706838483385</v>
       </c>
       <c r="CF56" s="18">
-        <v>2.1458759970018328</v>
+        <v>0.25411003739586174</v>
       </c>
       <c r="CG56" s="18">
-        <v>0.15060349122484992</v>
+        <v>0.42222696884749356</v>
       </c>
       <c r="CH56" s="18">
-        <v>1.4430063948018432</v>
+        <v>0.26166509261023935</v>
       </c>
       <c r="CI56" s="19">
-        <v>1.5945969694453055E-3</v>
+        <v>1.891180447344265E-4</v>
       </c>
       <c r="CJ56" s="19">
-        <v>2.0961455107149085E-4</v>
+        <v>2.2102370444976316E-7</v>
       </c>
       <c r="CK56" s="19">
-        <v>5.3267254271927023E-4</v>
+        <v>9.7238578066494163E-4</v>
       </c>
       <c r="CL56" s="20">
-        <v>1.5972500181847815E-3</v>
+        <v>1.5536835098722834E-3</v>
       </c>
       <c r="CM56" s="20">
-        <v>6.5929789385933413E-3</v>
+        <v>5.3573855420411265E-3</v>
       </c>
       <c r="CN56" s="20">
-        <v>2.2926889476613255E-3</v>
+        <v>7.7772585148982998E-4</v>
       </c>
       <c r="CS56" s="1">
         <v>48</v>
@@ -35096,27 +35138,27 @@
       </c>
       <c r="BW61" s="26">
         <f>AVERAGE(BW$9:BW$58)</f>
-        <v>3.1708054698461025E-2</v>
+        <v>2.5187149400354443E-2</v>
       </c>
       <c r="BX61" s="26">
         <f>AVERAGE(CC$9:CC$58)</f>
-        <v>0.91489866644652562</v>
+        <v>0.87915227224370118</v>
       </c>
       <c r="BY61" s="26">
         <f>AVERAGE(BZ$9:BZ$58)</f>
-        <v>0.55171624488197313</v>
+        <v>0.53991986787472024</v>
       </c>
       <c r="BZ61" s="26">
         <f>AVERAGE(CF$9:CF$58)</f>
-        <v>0.39145746541309273</v>
+        <v>0.31095246173276614</v>
       </c>
       <c r="CA61" s="26">
         <f>AVERAGE(CI$9:CI$58)</f>
-        <v>2.912151201625379E-4</v>
+        <v>2.3139767682546885E-4</v>
       </c>
       <c r="CB61" s="26">
         <f>AVERAGE(CL9:CL$58)</f>
-        <v>1.5665932257478855E-3</v>
+        <v>1.5175606732554115E-3</v>
       </c>
       <c r="CS61" s="23">
         <v>1</v>
@@ -35233,27 +35275,27 @@
       </c>
       <c r="BW62" s="26">
         <f>AVERAGE(BX$9:BX$58)</f>
-        <v>0.42130608621378796</v>
+        <v>0.42219598884605858</v>
       </c>
       <c r="BX62" s="26">
         <f>AVERAGE(CD$9:CD$58)</f>
-        <v>0.84202833638755858</v>
+        <v>0.86559721366277897</v>
       </c>
       <c r="BY62" s="26">
         <f>AVERAGE(CA$9:CA$58)</f>
-        <v>1.2612864587999946</v>
+        <v>1.2450734089052302</v>
       </c>
       <c r="BZ62" s="26">
         <f>AVERAGE(CG$9:CG$58)</f>
-        <v>0.41438328474331115</v>
+        <v>0.4249773636989182</v>
       </c>
       <c r="CA62" s="26">
         <f>AVERAGE(CJ$9:CJ$58)</f>
-        <v>1.9523507127199303E-5</v>
+        <v>1.231596769411647E-5</v>
       </c>
       <c r="CB62" s="26">
         <f>AVERAGE(CM10:CM$58)</f>
-        <v>5.4055127628596595E-3</v>
+        <v>5.3554221063705151E-3</v>
       </c>
       <c r="CS62" s="23">
         <v>0.75</v>
@@ -35370,27 +35412,27 @@
       </c>
       <c r="BW63" s="26">
         <f>AVERAGE(BY$9:BY$58)</f>
-        <v>0.74513000622539816</v>
+        <v>0.73790465950416517</v>
       </c>
       <c r="BX63" s="26">
         <f>AVERAGE(CE$9:CE$58)</f>
-        <v>0.20731605012714002</v>
+        <v>0.20880961926935107</v>
       </c>
       <c r="BY63" s="26">
         <f>AVERAGE(CB$9:CB$58)</f>
-        <v>0.88668720252318411</v>
+        <v>0.92244980086342498</v>
       </c>
       <c r="BZ63" s="26">
         <f>AVERAGE(CH$9:CH$58)</f>
-        <v>0.28910754931683291</v>
+        <v>0.24188000920531078</v>
       </c>
       <c r="CA63" s="26">
         <f>AVERAGE(CK$9:CK$58)</f>
-        <v>9.1263575915187186E-4</v>
+        <v>9.3181851444638973E-4</v>
       </c>
       <c r="CB63" s="26">
         <f>AVERAGE(CN11:CN$58)</f>
-        <v>8.7539893919115486E-4</v>
+        <v>7.8682496022633441E-4</v>
       </c>
       <c r="CS63" s="23">
         <v>0.5</v>
@@ -35421,7 +35463,7 @@
       </c>
     </row>
     <row r="65" spans="33:38" x14ac:dyDescent="0.25">
-      <c r="AG65" s="35" t="s">
+      <c r="AG65" s="42" t="s">
         <v>20</v>
       </c>
       <c r="AH65" s="27" t="s">
@@ -35432,7 +35474,7 @@
       </c>
     </row>
     <row r="66" spans="33:38" x14ac:dyDescent="0.25">
-      <c r="AG66" s="35"/>
+      <c r="AG66" s="42"/>
       <c r="AH66" s="29">
         <v>0.15</v>
       </c>
@@ -35600,32 +35642,6 @@
     </row>
   </sheetData>
   <mergeCells count="41">
-    <mergeCell ref="DI7:DK7"/>
-    <mergeCell ref="DA6:DJ6"/>
-    <mergeCell ref="CE6:CN6"/>
-    <mergeCell ref="CT7:CV7"/>
-    <mergeCell ref="CZ7:DB7"/>
-    <mergeCell ref="DC7:DE7"/>
-    <mergeCell ref="DF7:DH7"/>
-    <mergeCell ref="CW7:CY7"/>
-    <mergeCell ref="BP7:BR7"/>
-    <mergeCell ref="BW7:BY7"/>
-    <mergeCell ref="BZ7:CB7"/>
-    <mergeCell ref="CC7:CE7"/>
-    <mergeCell ref="CF7:CH7"/>
-    <mergeCell ref="CI7:CK7"/>
-    <mergeCell ref="CL7:CN7"/>
-    <mergeCell ref="AP7:AR7"/>
-    <mergeCell ref="K6:T6"/>
-    <mergeCell ref="AJ4:AN4"/>
-    <mergeCell ref="AS7:AU7"/>
-    <mergeCell ref="BF6:BO6"/>
-    <mergeCell ref="BA7:BC7"/>
-    <mergeCell ref="BD7:BF7"/>
-    <mergeCell ref="BG7:BI7"/>
-    <mergeCell ref="BJ7:BL7"/>
-    <mergeCell ref="BM7:BO7"/>
-    <mergeCell ref="BG4:BK4"/>
     <mergeCell ref="CC4:CF4"/>
     <mergeCell ref="CY4:DD4"/>
     <mergeCell ref="AG65:AG66"/>
@@ -35641,6 +35657,32 @@
     <mergeCell ref="AG7:AI7"/>
     <mergeCell ref="AJ7:AL7"/>
     <mergeCell ref="AM7:AO7"/>
+    <mergeCell ref="AP7:AR7"/>
+    <mergeCell ref="K6:T6"/>
+    <mergeCell ref="AJ4:AN4"/>
+    <mergeCell ref="AS7:AU7"/>
+    <mergeCell ref="BF6:BO6"/>
+    <mergeCell ref="BA7:BC7"/>
+    <mergeCell ref="BD7:BF7"/>
+    <mergeCell ref="BG7:BI7"/>
+    <mergeCell ref="BJ7:BL7"/>
+    <mergeCell ref="BM7:BO7"/>
+    <mergeCell ref="BG4:BK4"/>
+    <mergeCell ref="BP7:BR7"/>
+    <mergeCell ref="BW7:BY7"/>
+    <mergeCell ref="BZ7:CB7"/>
+    <mergeCell ref="CC7:CE7"/>
+    <mergeCell ref="CF7:CH7"/>
+    <mergeCell ref="DI7:DK7"/>
+    <mergeCell ref="DA6:DJ6"/>
+    <mergeCell ref="CE6:CN6"/>
+    <mergeCell ref="CT7:CV7"/>
+    <mergeCell ref="CZ7:DB7"/>
+    <mergeCell ref="DC7:DE7"/>
+    <mergeCell ref="DF7:DH7"/>
+    <mergeCell ref="CW7:CY7"/>
+    <mergeCell ref="CI7:CK7"/>
+    <mergeCell ref="CL7:CN7"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <drawing r:id="rId1"/>
@@ -35657,51 +35699,51 @@
   </cols>
   <sheetData>
     <row r="4" spans="6:115" x14ac:dyDescent="0.25">
-      <c r="L4" s="34" t="s">
+      <c r="L4" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="M4" s="34"/>
-      <c r="N4" s="34"/>
-      <c r="O4" s="34"/>
-      <c r="P4" s="34"/>
-      <c r="Q4" s="34"/>
-      <c r="R4" s="34"/>
-      <c r="AM4" s="34" t="s">
+      <c r="M4" s="41"/>
+      <c r="N4" s="41"/>
+      <c r="O4" s="41"/>
+      <c r="P4" s="41"/>
+      <c r="Q4" s="41"/>
+      <c r="R4" s="41"/>
+      <c r="AM4" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="AN4" s="34"/>
-      <c r="AO4" s="34"/>
-      <c r="AP4" s="34"/>
-      <c r="AQ4" s="34"/>
-      <c r="AR4" s="34"/>
-      <c r="AS4" s="34"/>
-      <c r="BI4" s="34" t="s">
+      <c r="AN4" s="41"/>
+      <c r="AO4" s="41"/>
+      <c r="AP4" s="41"/>
+      <c r="AQ4" s="41"/>
+      <c r="AR4" s="41"/>
+      <c r="AS4" s="41"/>
+      <c r="BI4" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="BJ4" s="34"/>
-      <c r="BK4" s="34"/>
-      <c r="BL4" s="34"/>
-      <c r="BM4" s="34"/>
-      <c r="BN4" s="34"/>
-      <c r="BO4" s="34"/>
-      <c r="CF4" s="34" t="s">
+      <c r="BJ4" s="41"/>
+      <c r="BK4" s="41"/>
+      <c r="BL4" s="41"/>
+      <c r="BM4" s="41"/>
+      <c r="BN4" s="41"/>
+      <c r="BO4" s="41"/>
+      <c r="CF4" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="CG4" s="34"/>
-      <c r="CH4" s="34"/>
-      <c r="CI4" s="34"/>
-      <c r="CJ4" s="34"/>
-      <c r="CK4" s="34"/>
-      <c r="CL4" s="34"/>
-      <c r="DB4" s="34" t="s">
+      <c r="CG4" s="41"/>
+      <c r="CH4" s="41"/>
+      <c r="CI4" s="41"/>
+      <c r="CJ4" s="41"/>
+      <c r="CK4" s="41"/>
+      <c r="CL4" s="41"/>
+      <c r="DB4" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="DC4" s="34"/>
-      <c r="DD4" s="34"/>
-      <c r="DE4" s="34"/>
-      <c r="DF4" s="34"/>
-      <c r="DG4" s="34"/>
-      <c r="DH4" s="34"/>
+      <c r="DC4" s="41"/>
+      <c r="DD4" s="41"/>
+      <c r="DE4" s="41"/>
+      <c r="DF4" s="41"/>
+      <c r="DG4" s="41"/>
+      <c r="DH4" s="41"/>
     </row>
     <row r="6" spans="6:115" ht="15.75" x14ac:dyDescent="0.25">
       <c r="F6" s="1"/>
@@ -35709,18 +35751,18 @@
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
-      <c r="K6" s="42" t="s">
+      <c r="K6" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="L6" s="42"/>
-      <c r="M6" s="42"/>
-      <c r="N6" s="42"/>
-      <c r="O6" s="42"/>
-      <c r="P6" s="42"/>
-      <c r="Q6" s="42"/>
-      <c r="R6" s="42"/>
-      <c r="S6" s="42"/>
-      <c r="T6" s="42"/>
+      <c r="L6" s="35"/>
+      <c r="M6" s="35"/>
+      <c r="N6" s="35"/>
+      <c r="O6" s="35"/>
+      <c r="P6" s="35"/>
+      <c r="Q6" s="35"/>
+      <c r="R6" s="35"/>
+      <c r="S6" s="35"/>
+      <c r="T6" s="35"/>
       <c r="U6" s="1"/>
       <c r="V6" s="1"/>
       <c r="W6" s="1"/>
@@ -35731,18 +35773,18 @@
       <c r="AF6" s="1"/>
       <c r="AG6" s="1"/>
       <c r="AH6" s="1"/>
-      <c r="AI6" s="42" t="s">
+      <c r="AI6" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="AJ6" s="42"/>
-      <c r="AK6" s="42"/>
-      <c r="AL6" s="42"/>
-      <c r="AM6" s="42"/>
-      <c r="AN6" s="42"/>
-      <c r="AO6" s="42"/>
-      <c r="AP6" s="42"/>
-      <c r="AQ6" s="42"/>
-      <c r="AR6" s="42"/>
+      <c r="AJ6" s="35"/>
+      <c r="AK6" s="35"/>
+      <c r="AL6" s="35"/>
+      <c r="AM6" s="35"/>
+      <c r="AN6" s="35"/>
+      <c r="AO6" s="35"/>
+      <c r="AP6" s="35"/>
+      <c r="AQ6" s="35"/>
+      <c r="AR6" s="35"/>
       <c r="AS6" s="1"/>
       <c r="AT6" s="1"/>
       <c r="AU6" s="1"/>
@@ -35752,18 +35794,18 @@
       <c r="BC6" s="1"/>
       <c r="BD6" s="1"/>
       <c r="BE6" s="1"/>
-      <c r="BF6" s="42" t="s">
+      <c r="BF6" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="BG6" s="42"/>
-      <c r="BH6" s="42"/>
-      <c r="BI6" s="42"/>
-      <c r="BJ6" s="42"/>
-      <c r="BK6" s="42"/>
-      <c r="BL6" s="42"/>
-      <c r="BM6" s="42"/>
-      <c r="BN6" s="42"/>
-      <c r="BO6" s="42"/>
+      <c r="BG6" s="35"/>
+      <c r="BH6" s="35"/>
+      <c r="BI6" s="35"/>
+      <c r="BJ6" s="35"/>
+      <c r="BK6" s="35"/>
+      <c r="BL6" s="35"/>
+      <c r="BM6" s="35"/>
+      <c r="BN6" s="35"/>
+      <c r="BO6" s="35"/>
       <c r="BP6" s="1"/>
       <c r="BQ6" s="1"/>
       <c r="BR6" s="1"/>
@@ -35776,30 +35818,30 @@
       <c r="CB6" s="1"/>
       <c r="CC6" s="1"/>
       <c r="CD6" s="1"/>
-      <c r="CE6" s="42" t="s">
+      <c r="CE6" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="CF6" s="42"/>
-      <c r="CG6" s="42"/>
-      <c r="CH6" s="42"/>
-      <c r="CI6" s="42"/>
-      <c r="CJ6" s="42"/>
-      <c r="CK6" s="42"/>
-      <c r="CL6" s="42"/>
-      <c r="CM6" s="42"/>
-      <c r="CN6" s="42"/>
-      <c r="DA6" s="42" t="s">
+      <c r="CF6" s="35"/>
+      <c r="CG6" s="35"/>
+      <c r="CH6" s="35"/>
+      <c r="CI6" s="35"/>
+      <c r="CJ6" s="35"/>
+      <c r="CK6" s="35"/>
+      <c r="CL6" s="35"/>
+      <c r="CM6" s="35"/>
+      <c r="CN6" s="35"/>
+      <c r="DA6" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="DB6" s="42"/>
-      <c r="DC6" s="42"/>
-      <c r="DD6" s="42"/>
-      <c r="DE6" s="42"/>
-      <c r="DF6" s="42"/>
-      <c r="DG6" s="42"/>
-      <c r="DH6" s="42"/>
-      <c r="DI6" s="42"/>
-      <c r="DJ6" s="42"/>
+      <c r="DB6" s="35"/>
+      <c r="DC6" s="35"/>
+      <c r="DD6" s="35"/>
+      <c r="DE6" s="35"/>
+      <c r="DF6" s="35"/>
+      <c r="DG6" s="35"/>
+      <c r="DH6" s="35"/>
+      <c r="DI6" s="35"/>
+      <c r="DJ6" s="35"/>
     </row>
     <row r="7" spans="6:115" ht="15.75" x14ac:dyDescent="0.25">
       <c r="F7" s="1"/>
@@ -35808,155 +35850,155 @@
       </c>
       <c r="H7" s="36"/>
       <c r="I7" s="36"/>
-      <c r="J7" s="37" t="s">
+      <c r="J7" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="K7" s="37"/>
-      <c r="L7" s="37"/>
-      <c r="M7" s="38" t="s">
+      <c r="K7" s="40"/>
+      <c r="L7" s="40"/>
+      <c r="M7" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="N7" s="38"/>
-      <c r="O7" s="38"/>
-      <c r="P7" s="39" t="s">
+      <c r="N7" s="37"/>
+      <c r="O7" s="37"/>
+      <c r="P7" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="Q7" s="39"/>
-      <c r="R7" s="39"/>
-      <c r="S7" s="40" t="s">
+      <c r="Q7" s="38"/>
+      <c r="R7" s="38"/>
+      <c r="S7" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="T7" s="40"/>
-      <c r="U7" s="40"/>
-      <c r="V7" s="41" t="s">
+      <c r="T7" s="39"/>
+      <c r="U7" s="39"/>
+      <c r="V7" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="W7" s="41"/>
-      <c r="X7" s="41"/>
+      <c r="W7" s="34"/>
+      <c r="X7" s="34"/>
       <c r="AC7" s="1"/>
       <c r="AD7" s="36" t="s">
         <v>1</v>
       </c>
       <c r="AE7" s="36"/>
       <c r="AF7" s="36"/>
-      <c r="AG7" s="37" t="s">
+      <c r="AG7" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="AH7" s="37"/>
-      <c r="AI7" s="37"/>
-      <c r="AJ7" s="38" t="s">
+      <c r="AH7" s="40"/>
+      <c r="AI7" s="40"/>
+      <c r="AJ7" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="AK7" s="38"/>
-      <c r="AL7" s="38"/>
-      <c r="AM7" s="39" t="s">
+      <c r="AK7" s="37"/>
+      <c r="AL7" s="37"/>
+      <c r="AM7" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="AN7" s="39"/>
-      <c r="AO7" s="39"/>
-      <c r="AP7" s="40" t="s">
+      <c r="AN7" s="38"/>
+      <c r="AO7" s="38"/>
+      <c r="AP7" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="AQ7" s="40"/>
-      <c r="AR7" s="40"/>
-      <c r="AS7" s="41" t="s">
+      <c r="AQ7" s="39"/>
+      <c r="AR7" s="39"/>
+      <c r="AS7" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="AT7" s="41"/>
-      <c r="AU7" s="41"/>
+      <c r="AT7" s="34"/>
+      <c r="AU7" s="34"/>
       <c r="AZ7" s="1"/>
       <c r="BA7" s="36" t="s">
         <v>1</v>
       </c>
       <c r="BB7" s="36"/>
       <c r="BC7" s="36"/>
-      <c r="BD7" s="37" t="s">
+      <c r="BD7" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="BE7" s="37"/>
-      <c r="BF7" s="37"/>
-      <c r="BG7" s="38" t="s">
+      <c r="BE7" s="40"/>
+      <c r="BF7" s="40"/>
+      <c r="BG7" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="BH7" s="38"/>
-      <c r="BI7" s="38"/>
-      <c r="BJ7" s="39" t="s">
+      <c r="BH7" s="37"/>
+      <c r="BI7" s="37"/>
+      <c r="BJ7" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="BK7" s="39"/>
-      <c r="BL7" s="39"/>
-      <c r="BM7" s="40" t="s">
+      <c r="BK7" s="38"/>
+      <c r="BL7" s="38"/>
+      <c r="BM7" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="BN7" s="40"/>
-      <c r="BO7" s="40"/>
-      <c r="BP7" s="41" t="s">
+      <c r="BN7" s="39"/>
+      <c r="BO7" s="39"/>
+      <c r="BP7" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="BQ7" s="41"/>
-      <c r="BR7" s="41"/>
+      <c r="BQ7" s="34"/>
+      <c r="BR7" s="34"/>
       <c r="BV7" s="1"/>
       <c r="BW7" s="36" t="s">
         <v>1</v>
       </c>
       <c r="BX7" s="36"/>
       <c r="BY7" s="36"/>
-      <c r="BZ7" s="37" t="s">
+      <c r="BZ7" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="CA7" s="37"/>
-      <c r="CB7" s="37"/>
-      <c r="CC7" s="38" t="s">
+      <c r="CA7" s="40"/>
+      <c r="CB7" s="40"/>
+      <c r="CC7" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="CD7" s="38"/>
-      <c r="CE7" s="38"/>
-      <c r="CF7" s="39" t="s">
+      <c r="CD7" s="37"/>
+      <c r="CE7" s="37"/>
+      <c r="CF7" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="CG7" s="39"/>
-      <c r="CH7" s="39"/>
-      <c r="CI7" s="40" t="s">
+      <c r="CG7" s="38"/>
+      <c r="CH7" s="38"/>
+      <c r="CI7" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="CJ7" s="40"/>
-      <c r="CK7" s="40"/>
-      <c r="CL7" s="41" t="s">
+      <c r="CJ7" s="39"/>
+      <c r="CK7" s="39"/>
+      <c r="CL7" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="CM7" s="41"/>
-      <c r="CN7" s="41"/>
+      <c r="CM7" s="34"/>
+      <c r="CN7" s="34"/>
       <c r="CS7" s="1"/>
       <c r="CT7" s="36" t="s">
         <v>1</v>
       </c>
       <c r="CU7" s="36"/>
       <c r="CV7" s="36"/>
-      <c r="CW7" s="37" t="s">
+      <c r="CW7" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="CX7" s="37"/>
-      <c r="CY7" s="37"/>
-      <c r="CZ7" s="38" t="s">
+      <c r="CX7" s="40"/>
+      <c r="CY7" s="40"/>
+      <c r="CZ7" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="DA7" s="38"/>
-      <c r="DB7" s="38"/>
-      <c r="DC7" s="39" t="s">
+      <c r="DA7" s="37"/>
+      <c r="DB7" s="37"/>
+      <c r="DC7" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="DD7" s="39"/>
-      <c r="DE7" s="39"/>
-      <c r="DF7" s="40" t="s">
+      <c r="DD7" s="38"/>
+      <c r="DE7" s="38"/>
+      <c r="DF7" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="DG7" s="40"/>
-      <c r="DH7" s="40"/>
-      <c r="DI7" s="41" t="s">
+      <c r="DG7" s="39"/>
+      <c r="DH7" s="39"/>
+      <c r="DI7" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="DJ7" s="41"/>
-      <c r="DK7" s="41"/>
+      <c r="DJ7" s="34"/>
+      <c r="DK7" s="34"/>
     </row>
     <row r="8" spans="6:115" ht="15.75" x14ac:dyDescent="0.25">
       <c r="F8" s="1" t="s">
@@ -51017,12 +51059,24 @@
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="DB4:DH4"/>
-    <mergeCell ref="K6:T6"/>
-    <mergeCell ref="AI6:AR6"/>
-    <mergeCell ref="BF6:BO6"/>
-    <mergeCell ref="CE6:CN6"/>
-    <mergeCell ref="DA6:DJ6"/>
+    <mergeCell ref="BM7:BO7"/>
+    <mergeCell ref="DI7:DK7"/>
+    <mergeCell ref="BW7:BY7"/>
+    <mergeCell ref="BZ7:CB7"/>
+    <mergeCell ref="CC7:CE7"/>
+    <mergeCell ref="CF7:CH7"/>
+    <mergeCell ref="CI7:CK7"/>
+    <mergeCell ref="CL7:CN7"/>
+    <mergeCell ref="CT7:CV7"/>
+    <mergeCell ref="CW7:CY7"/>
+    <mergeCell ref="CZ7:DB7"/>
+    <mergeCell ref="DC7:DE7"/>
+    <mergeCell ref="DF7:DH7"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="M7:O7"/>
+    <mergeCell ref="P7:R7"/>
+    <mergeCell ref="S7:U7"/>
     <mergeCell ref="V7:X7"/>
     <mergeCell ref="L4:R4"/>
     <mergeCell ref="AM4:AS4"/>
@@ -51039,24 +51093,12 @@
     <mergeCell ref="BD7:BF7"/>
     <mergeCell ref="BG7:BI7"/>
     <mergeCell ref="BJ7:BL7"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="M7:O7"/>
-    <mergeCell ref="P7:R7"/>
-    <mergeCell ref="S7:U7"/>
-    <mergeCell ref="BM7:BO7"/>
-    <mergeCell ref="DI7:DK7"/>
-    <mergeCell ref="BW7:BY7"/>
-    <mergeCell ref="BZ7:CB7"/>
-    <mergeCell ref="CC7:CE7"/>
-    <mergeCell ref="CF7:CH7"/>
-    <mergeCell ref="CI7:CK7"/>
-    <mergeCell ref="CL7:CN7"/>
-    <mergeCell ref="CT7:CV7"/>
-    <mergeCell ref="CW7:CY7"/>
-    <mergeCell ref="CZ7:DB7"/>
-    <mergeCell ref="DC7:DE7"/>
-    <mergeCell ref="DF7:DH7"/>
+    <mergeCell ref="DB4:DH4"/>
+    <mergeCell ref="K6:T6"/>
+    <mergeCell ref="AI6:AR6"/>
+    <mergeCell ref="BF6:BO6"/>
+    <mergeCell ref="CE6:CN6"/>
+    <mergeCell ref="DA6:DJ6"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <drawing r:id="rId1"/>
